--- a/hackground/public/assets/defaults/city_excel_format/city_excel_format.xlsx
+++ b/hackground/public/assets/defaults/city_excel_format/city_excel_format.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="587">
   <si>
     <t>name_en</t>
   </si>
@@ -1682,13 +1682,106 @@
   </si>
   <si>
     <t>رودرا بور</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Andhra Pradesh</t>
+  </si>
+  <si>
+    <t>India1</t>
+  </si>
+  <si>
+    <t>Assam</t>
+  </si>
+  <si>
+    <t>West Bengal</t>
+  </si>
+  <si>
+    <t>Arunachal Pradesh</t>
+  </si>
+  <si>
+    <t>Bihar</t>
+  </si>
+  <si>
+    <t>Chhattisgarh</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gujarat </t>
+  </si>
+  <si>
+    <t>Haryana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Himachal Pradesh </t>
+  </si>
+  <si>
+    <t>Jharkhand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karnataka </t>
+  </si>
+  <si>
+    <t>Kerala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madhya Pradesh </t>
+  </si>
+  <si>
+    <t>Maharashtra</t>
+  </si>
+  <si>
+    <t>Manipur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meghalaya </t>
+  </si>
+  <si>
+    <t>Mizoram</t>
+  </si>
+  <si>
+    <t>vIndia</t>
+  </si>
+  <si>
+    <t>Nagaland</t>
+  </si>
+  <si>
+    <t>Odisha</t>
+  </si>
+  <si>
+    <t>Punjab</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
+  </si>
+  <si>
+    <t>Sikkim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamil Nadu </t>
+  </si>
+  <si>
+    <t>Telangana</t>
+  </si>
+  <si>
+    <t>Tripura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uttar Pradesh </t>
+  </si>
+  <si>
+    <t>Uttarakhand</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1704,13 +1797,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1740,7 +1851,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1751,6 +1862,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2046,12 +2166,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G281"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" customWidth="1"/>
+    <col min="1" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2069,11 +2189,11 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B2" t="s">
+        <v>557</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2084,11 +2204,11 @@
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="A3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B3" t="s">
+        <v>557</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2098,11 +2218,11 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="A4" t="s">
+        <v>556</v>
+      </c>
+      <c r="B4" t="s">
+        <v>557</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -2112,11 +2232,11 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="A5" t="s">
+        <v>556</v>
+      </c>
+      <c r="B5" t="s">
+        <v>557</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -2126,11 +2246,11 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="A6" t="s">
+        <v>556</v>
+      </c>
+      <c r="B6" t="s">
+        <v>557</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -2140,11 +2260,11 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
+      <c r="A7" t="s">
+        <v>556</v>
+      </c>
+      <c r="B7" t="s">
+        <v>557</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -2154,11 +2274,11 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
+      <c r="A8" t="s">
+        <v>558</v>
+      </c>
+      <c r="B8" t="s">
+        <v>557</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -2168,11 +2288,11 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
+      <c r="A9" t="s">
+        <v>556</v>
+      </c>
+      <c r="B9" t="s">
+        <v>557</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -2182,11 +2302,11 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
+      <c r="A10" t="s">
+        <v>556</v>
+      </c>
+      <c r="B10" t="s">
+        <v>557</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -2196,11 +2316,11 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
+      <c r="A11" t="s">
+        <v>556</v>
+      </c>
+      <c r="B11" t="s">
+        <v>557</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
@@ -2210,151 +2330,151 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="2">
-        <v>1</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="A12" t="s">
+        <v>556</v>
+      </c>
+      <c r="B12" t="s">
+        <v>559</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="2">
-        <v>1</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="A13" t="s">
+        <v>556</v>
+      </c>
+      <c r="B13" t="s">
+        <v>559</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="2">
-        <v>1</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="A14" t="s">
+        <v>556</v>
+      </c>
+      <c r="B14" t="s">
+        <v>559</v>
+      </c>
+      <c r="C14" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="2">
-        <v>1</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="A15" t="s">
+        <v>556</v>
+      </c>
+      <c r="B15" t="s">
+        <v>559</v>
+      </c>
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="2">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2">
-        <v>2</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="A16" t="s">
+        <v>556</v>
+      </c>
+      <c r="B16" t="s">
+        <v>559</v>
+      </c>
+      <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="2">
-        <v>1</v>
-      </c>
-      <c r="B17" s="2">
-        <v>2</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="A17" t="s">
+        <v>556</v>
+      </c>
+      <c r="B17" t="s">
+        <v>559</v>
+      </c>
+      <c r="C17" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="2">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2">
-        <v>2</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="A18" t="s">
+        <v>556</v>
+      </c>
+      <c r="B18" t="s">
+        <v>559</v>
+      </c>
+      <c r="C18" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="2">
-        <v>1</v>
-      </c>
-      <c r="B19" s="2">
-        <v>2</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="A19" t="s">
+        <v>556</v>
+      </c>
+      <c r="B19" t="s">
+        <v>559</v>
+      </c>
+      <c r="C19" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="2">
-        <v>1</v>
-      </c>
-      <c r="B20" s="2">
-        <v>2</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="A20" t="s">
+        <v>556</v>
+      </c>
+      <c r="B20" t="s">
+        <v>559</v>
+      </c>
+      <c r="C20" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="2">
-        <v>1</v>
-      </c>
-      <c r="B21" s="2">
-        <v>2</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="A21" t="s">
+        <v>556</v>
+      </c>
+      <c r="B21" t="s">
+        <v>559</v>
+      </c>
+      <c r="C21" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
+    <row r="22" spans="1:4" ht="16.8">
+      <c r="A22" t="s">
+        <v>556</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C22" t="s">
         <v>44</v>
@@ -2363,12 +2483,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23">
-        <v>1</v>
-      </c>
-      <c r="B23">
-        <v>3</v>
+    <row r="23" spans="1:4" ht="16.8">
+      <c r="A23" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C23" t="s">
         <v>46</v>
@@ -2377,12 +2497,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
+    <row r="24" spans="1:4" ht="16.8">
+      <c r="A24" t="s">
+        <v>556</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C24" t="s">
         <v>48</v>
@@ -2391,12 +2511,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25">
-        <v>1</v>
-      </c>
-      <c r="B25">
-        <v>3</v>
+    <row r="25" spans="1:4" ht="16.8">
+      <c r="A25" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C25" t="s">
         <v>50</v>
@@ -2405,12 +2525,12 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26">
-        <v>1</v>
-      </c>
-      <c r="B26">
-        <v>3</v>
+    <row r="26" spans="1:4" ht="16.8">
+      <c r="A26" t="s">
+        <v>556</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C26" t="s">
         <v>52</v>
@@ -2419,12 +2539,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27">
-        <v>1</v>
-      </c>
-      <c r="B27">
-        <v>3</v>
+    <row r="27" spans="1:4" ht="16.8">
+      <c r="A27" t="s">
+        <v>556</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C27" t="s">
         <v>54</v>
@@ -2433,12 +2553,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28">
-        <v>1</v>
-      </c>
-      <c r="B28">
-        <v>3</v>
+    <row r="28" spans="1:4" ht="16.8">
+      <c r="A28" t="s">
+        <v>556</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C28" t="s">
         <v>56</v>
@@ -2447,12 +2567,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29">
-        <v>1</v>
-      </c>
-      <c r="B29">
-        <v>3</v>
+    <row r="29" spans="1:4" ht="16.8">
+      <c r="A29" t="s">
+        <v>556</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C29" t="s">
         <v>58</v>
@@ -2461,12 +2581,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30">
-        <v>1</v>
-      </c>
-      <c r="B30">
-        <v>3</v>
+    <row r="30" spans="1:4" ht="16.8">
+      <c r="A30" t="s">
+        <v>556</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C30" t="s">
         <v>60</v>
@@ -2475,12 +2595,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31">
-        <v>1</v>
-      </c>
-      <c r="B31">
-        <v>3</v>
+    <row r="31" spans="1:4" ht="16.8">
+      <c r="A31" t="s">
+        <v>556</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>560</v>
       </c>
       <c r="C31" t="s">
         <v>62</v>
@@ -2489,12 +2609,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32">
-        <v>1</v>
-      </c>
-      <c r="B32">
-        <v>5</v>
+    <row r="32" spans="1:4" ht="16.8">
+      <c r="A32" t="s">
+        <v>556</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C32" t="s">
         <v>64</v>
@@ -2503,12 +2623,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
-      <c r="A33">
-        <v>1</v>
-      </c>
-      <c r="B33">
-        <v>5</v>
+    <row r="33" spans="1:4" ht="16.8">
+      <c r="A33" t="s">
+        <v>556</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C33" t="s">
         <v>66</v>
@@ -2517,12 +2637,12 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="B34">
-        <v>5</v>
+    <row r="34" spans="1:4" ht="16.8">
+      <c r="A34" t="s">
+        <v>556</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C34" t="s">
         <v>68</v>
@@ -2531,12 +2651,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35">
-        <v>1</v>
-      </c>
-      <c r="B35">
-        <v>5</v>
+    <row r="35" spans="1:4" ht="16.8">
+      <c r="A35" t="s">
+        <v>556</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C35" t="s">
         <v>70</v>
@@ -2545,12 +2665,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36">
-        <v>1</v>
-      </c>
-      <c r="B36">
-        <v>5</v>
+    <row r="36" spans="1:4" ht="16.8">
+      <c r="A36" t="s">
+        <v>556</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C36" t="s">
         <v>72</v>
@@ -2559,12 +2679,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37">
-        <v>1</v>
-      </c>
-      <c r="B37">
-        <v>5</v>
+    <row r="37" spans="1:4" ht="16.8">
+      <c r="A37" t="s">
+        <v>556</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C37" t="s">
         <v>74</v>
@@ -2573,12 +2693,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38">
-        <v>1</v>
-      </c>
-      <c r="B38">
-        <v>5</v>
+    <row r="38" spans="1:4" ht="16.8">
+      <c r="A38" t="s">
+        <v>556</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C38" t="s">
         <v>76</v>
@@ -2587,12 +2707,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
-      <c r="A39">
-        <v>1</v>
-      </c>
-      <c r="B39">
-        <v>5</v>
+    <row r="39" spans="1:4" ht="16.8">
+      <c r="A39" t="s">
+        <v>556</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C39" t="s">
         <v>78</v>
@@ -2601,12 +2721,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
-      <c r="A40">
-        <v>1</v>
-      </c>
-      <c r="B40">
-        <v>5</v>
+    <row r="40" spans="1:4" ht="16.8">
+      <c r="A40" t="s">
+        <v>556</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C40" t="s">
         <v>80</v>
@@ -2615,12 +2735,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
-      <c r="A41">
-        <v>1</v>
-      </c>
-      <c r="B41">
-        <v>5</v>
+    <row r="41" spans="1:4" ht="16.8">
+      <c r="A41" t="s">
+        <v>556</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>561</v>
       </c>
       <c r="C41" t="s">
         <v>82</v>
@@ -2629,12 +2749,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="3">
-        <v>1</v>
-      </c>
-      <c r="B42" s="3">
-        <v>6</v>
+    <row r="42" spans="1:4" ht="16.8">
+      <c r="A42" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>84</v>
@@ -2643,12 +2763,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="3">
-        <v>1</v>
-      </c>
-      <c r="B43" s="3">
-        <v>6</v>
+    <row r="43" spans="1:4" ht="16.8">
+      <c r="A43" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>86</v>
@@ -2657,12 +2777,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="3">
-        <v>1</v>
-      </c>
-      <c r="B44" s="3">
-        <v>6</v>
+    <row r="44" spans="1:4" ht="16.8">
+      <c r="A44" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>88</v>
@@ -2671,12 +2791,12 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="3">
-        <v>1</v>
-      </c>
-      <c r="B45" s="3">
-        <v>6</v>
+    <row r="45" spans="1:4" ht="16.8">
+      <c r="A45" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>90</v>
@@ -2685,12 +2805,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="3">
-        <v>1</v>
-      </c>
-      <c r="B46" s="3">
-        <v>6</v>
+    <row r="46" spans="1:4" ht="16.8">
+      <c r="A46" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>92</v>
@@ -2699,12 +2819,12 @@
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="3">
-        <v>1</v>
-      </c>
-      <c r="B47" s="3">
-        <v>6</v>
+    <row r="47" spans="1:4" ht="16.8">
+      <c r="A47" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>94</v>
@@ -2713,12 +2833,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="3">
-        <v>1</v>
-      </c>
-      <c r="B48" s="3">
-        <v>6</v>
+    <row r="48" spans="1:4" ht="16.8">
+      <c r="A48" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>96</v>
@@ -2727,12 +2847,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="3">
-        <v>1</v>
-      </c>
-      <c r="B49" s="3">
-        <v>6</v>
+    <row r="49" spans="1:4" ht="16.8">
+      <c r="A49" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>98</v>
@@ -2741,12 +2861,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="3">
-        <v>1</v>
-      </c>
-      <c r="B50" s="3">
-        <v>6</v>
+    <row r="50" spans="1:4" ht="16.8">
+      <c r="A50" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>100</v>
@@ -2755,12 +2875,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="3">
-        <v>1</v>
-      </c>
-      <c r="B51" s="3">
-        <v>6</v>
+    <row r="51" spans="1:4" ht="16.8">
+      <c r="A51" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>562</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>102</v>
@@ -2769,12 +2889,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="3">
-        <v>1</v>
-      </c>
-      <c r="B52" s="3">
-        <v>7</v>
+    <row r="52" spans="1:4" ht="16.8">
+      <c r="A52" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>104</v>
@@ -2783,12 +2903,12 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="3">
-        <v>1</v>
-      </c>
-      <c r="B53" s="3">
-        <v>7</v>
+    <row r="53" spans="1:4" ht="16.8">
+      <c r="A53" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>106</v>
@@ -2797,12 +2917,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="3">
-        <v>1</v>
-      </c>
-      <c r="B54" s="3">
-        <v>7</v>
+    <row r="54" spans="1:4" ht="16.8">
+      <c r="A54" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>108</v>
@@ -2811,12 +2931,12 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="3">
-        <v>1</v>
-      </c>
-      <c r="B55" s="3">
-        <v>7</v>
+    <row r="55" spans="1:4" ht="16.8">
+      <c r="A55" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>110</v>
@@ -2825,12 +2945,12 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="3">
-        <v>1</v>
-      </c>
-      <c r="B56" s="3">
-        <v>7</v>
+    <row r="56" spans="1:4" ht="16.8">
+      <c r="A56" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>112</v>
@@ -2839,12 +2959,12 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="3">
-        <v>1</v>
-      </c>
-      <c r="B57" s="3">
-        <v>7</v>
+    <row r="57" spans="1:4" ht="16.8">
+      <c r="A57" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>114</v>
@@ -2853,12 +2973,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="3">
-        <v>1</v>
-      </c>
-      <c r="B58" s="3">
-        <v>7</v>
+    <row r="58" spans="1:4" ht="16.8">
+      <c r="A58" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>116</v>
@@ -2867,12 +2987,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="3">
-        <v>1</v>
-      </c>
-      <c r="B59" s="3">
-        <v>7</v>
+    <row r="59" spans="1:4" ht="16.8">
+      <c r="A59" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>118</v>
@@ -2881,12 +3001,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="3">
-        <v>1</v>
-      </c>
-      <c r="B60" s="3">
-        <v>7</v>
+    <row r="60" spans="1:4" ht="16.8">
+      <c r="A60" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>120</v>
@@ -2895,12 +3015,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="3">
-        <v>1</v>
-      </c>
-      <c r="B61" s="3">
-        <v>7</v>
+    <row r="61" spans="1:4" ht="16.8">
+      <c r="A61" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>122</v>
@@ -2909,12 +3029,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="3">
-        <v>1</v>
-      </c>
-      <c r="B62" s="3">
-        <v>8</v>
+    <row r="62" spans="1:4" ht="16.8">
+      <c r="A62" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>124</v>
@@ -2923,12 +3043,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="3">
-        <v>1</v>
-      </c>
-      <c r="B63" s="3">
-        <v>8</v>
+    <row r="63" spans="1:4" ht="16.8">
+      <c r="A63" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>563</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>126</v>
@@ -2938,11 +3058,11 @@
       </c>
     </row>
     <row r="64" spans="1:4" ht="30">
-      <c r="A64" s="3">
-        <v>1</v>
-      </c>
-      <c r="B64" s="3">
-        <v>8</v>
+      <c r="A64" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>564</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>128</v>
@@ -2951,12 +3071,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="3">
-        <v>1</v>
-      </c>
-      <c r="B65" s="3">
-        <v>8</v>
+    <row r="65" spans="1:4" ht="16.8">
+      <c r="A65" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>564</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>130</v>
@@ -2965,12 +3085,12 @@
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="3">
-        <v>1</v>
-      </c>
-      <c r="B66" s="3">
-        <v>8</v>
+    <row r="66" spans="1:4" ht="16.8">
+      <c r="A66" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>564</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>132</v>
@@ -2979,12 +3099,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="3">
-        <v>1</v>
-      </c>
-      <c r="B67" s="3">
-        <v>8</v>
+    <row r="67" spans="1:4" ht="16.8">
+      <c r="A67" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>564</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>134</v>
@@ -2993,12 +3113,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="3">
-        <v>1</v>
-      </c>
-      <c r="B68" s="3">
-        <v>8</v>
+    <row r="68" spans="1:4" ht="16.8">
+      <c r="A68" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>564</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>136</v>
@@ -3007,12 +3127,12 @@
         <v>137</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="3">
-        <v>1</v>
-      </c>
-      <c r="B69" s="3">
-        <v>8</v>
+    <row r="69" spans="1:4" ht="16.8">
+      <c r="A69" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>564</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>138</v>
@@ -3021,12 +3141,12 @@
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="3">
-        <v>1</v>
-      </c>
-      <c r="B70" s="3">
-        <v>8</v>
+    <row r="70" spans="1:4" ht="16.8">
+      <c r="A70" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>564</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>140</v>
@@ -3035,12 +3155,12 @@
         <v>141</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="3">
-        <v>1</v>
-      </c>
-      <c r="B71" s="3">
-        <v>8</v>
+    <row r="71" spans="1:4" ht="16.8">
+      <c r="A71" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>564</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>142</v>
@@ -3050,11 +3170,11 @@
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="3">
-        <v>1</v>
-      </c>
-      <c r="B72" s="3">
-        <v>9</v>
+      <c r="A72" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>144</v>
@@ -3064,11 +3184,11 @@
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="3">
-        <v>1</v>
-      </c>
-      <c r="B73" s="3">
-        <v>9</v>
+      <c r="A73" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>146</v>
@@ -3078,11 +3198,11 @@
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="3">
-        <v>1</v>
-      </c>
-      <c r="B74" s="3">
-        <v>9</v>
+      <c r="A74" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>148</v>
@@ -3092,11 +3212,11 @@
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="3">
-        <v>1</v>
-      </c>
-      <c r="B75" s="3">
-        <v>9</v>
+      <c r="A75" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>150</v>
@@ -3106,11 +3226,11 @@
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="3">
-        <v>1</v>
-      </c>
-      <c r="B76" s="3">
-        <v>9</v>
+      <c r="A76" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>152</v>
@@ -3120,11 +3240,11 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="3">
-        <v>1</v>
-      </c>
-      <c r="B77" s="3">
-        <v>9</v>
+      <c r="A77" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>154</v>
@@ -3134,11 +3254,11 @@
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="3">
-        <v>1</v>
-      </c>
-      <c r="B78" s="3">
-        <v>9</v>
+      <c r="A78" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>156</v>
@@ -3148,11 +3268,11 @@
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="3">
-        <v>1</v>
-      </c>
-      <c r="B79" s="3">
-        <v>9</v>
+      <c r="A79" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>158</v>
@@ -3162,11 +3282,11 @@
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="3">
-        <v>1</v>
-      </c>
-      <c r="B80" s="3">
-        <v>9</v>
+      <c r="A80" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>160</v>
@@ -3176,11 +3296,11 @@
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="3">
-        <v>1</v>
-      </c>
-      <c r="B81" s="3">
-        <v>9</v>
+      <c r="A81" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>565</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>162</v>
@@ -3190,11 +3310,11 @@
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="3">
-        <v>1</v>
-      </c>
-      <c r="B82" s="3">
-        <v>10</v>
+      <c r="A82" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>566</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>164</v>
@@ -3203,12 +3323,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="3">
-        <v>1</v>
-      </c>
-      <c r="B83" s="3">
-        <v>10</v>
+    <row r="83" spans="1:4" ht="16.8">
+      <c r="A83" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>166</v>
@@ -3217,12 +3337,12 @@
         <v>167</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="3">
-        <v>1</v>
-      </c>
-      <c r="B84" s="3">
-        <v>10</v>
+    <row r="84" spans="1:4" ht="16.8">
+      <c r="A84" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>168</v>
@@ -3231,12 +3351,12 @@
         <v>169</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="3">
-        <v>1</v>
-      </c>
-      <c r="B85" s="3">
-        <v>10</v>
+    <row r="85" spans="1:4" ht="16.8">
+      <c r="A85" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>170</v>
@@ -3245,12 +3365,12 @@
         <v>171</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="3">
-        <v>1</v>
-      </c>
-      <c r="B86" s="3">
-        <v>10</v>
+    <row r="86" spans="1:4" ht="16.8">
+      <c r="A86" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>172</v>
@@ -3259,12 +3379,12 @@
         <v>173</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="3">
-        <v>1</v>
-      </c>
-      <c r="B87" s="3">
-        <v>10</v>
+    <row r="87" spans="1:4" ht="16.8">
+      <c r="A87" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>174</v>
@@ -3273,12 +3393,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="3">
-        <v>1</v>
-      </c>
-      <c r="B88" s="3">
-        <v>10</v>
+    <row r="88" spans="1:4" ht="16.8">
+      <c r="A88" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>176</v>
@@ -3287,12 +3407,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="3">
-        <v>1</v>
-      </c>
-      <c r="B89" s="3">
-        <v>10</v>
+    <row r="89" spans="1:4" ht="16.8">
+      <c r="A89" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>178</v>
@@ -3301,12 +3421,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="3">
-        <v>1</v>
-      </c>
-      <c r="B90" s="3">
-        <v>10</v>
+    <row r="90" spans="1:4" ht="16.8">
+      <c r="A90" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>180</v>
@@ -3315,12 +3435,12 @@
         <v>181</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="3">
-        <v>1</v>
-      </c>
-      <c r="B91" s="3">
-        <v>10</v>
+    <row r="91" spans="1:4" ht="16.8">
+      <c r="A91" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>566</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>182</v>
@@ -3329,12 +3449,12 @@
         <v>183</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="3">
-        <v>1</v>
-      </c>
-      <c r="B92" s="3">
-        <v>11</v>
+    <row r="92" spans="1:4" ht="28.8">
+      <c r="A92" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>184</v>
@@ -3343,12 +3463,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="3">
-        <v>1</v>
-      </c>
-      <c r="B93" s="3">
-        <v>11</v>
+    <row r="93" spans="1:4" ht="28.8">
+      <c r="A93" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>186</v>
@@ -3357,12 +3477,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="3">
-        <v>1</v>
-      </c>
-      <c r="B94" s="3">
-        <v>11</v>
+    <row r="94" spans="1:4" ht="28.8">
+      <c r="A94" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>188</v>
@@ -3371,12 +3491,12 @@
         <v>189</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="3">
-        <v>1</v>
-      </c>
-      <c r="B95" s="3">
-        <v>11</v>
+    <row r="95" spans="1:4" ht="28.8">
+      <c r="A95" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>190</v>
@@ -3385,12 +3505,12 @@
         <v>191</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="3">
-        <v>1</v>
-      </c>
-      <c r="B96" s="3">
-        <v>11</v>
+    <row r="96" spans="1:4" ht="28.8">
+      <c r="A96" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>192</v>
@@ -3399,12 +3519,12 @@
         <v>193</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="3">
-        <v>1</v>
-      </c>
-      <c r="B97" s="3">
-        <v>11</v>
+    <row r="97" spans="1:4" ht="28.8">
+      <c r="A97" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>194</v>
@@ -3413,12 +3533,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="3">
-        <v>1</v>
-      </c>
-      <c r="B98" s="3">
-        <v>11</v>
+    <row r="98" spans="1:4" ht="28.8">
+      <c r="A98" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>196</v>
@@ -3427,12 +3547,12 @@
         <v>197</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="3">
-        <v>1</v>
-      </c>
-      <c r="B99" s="3">
-        <v>11</v>
+    <row r="99" spans="1:4" ht="28.8">
+      <c r="A99" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>198</v>
@@ -3441,12 +3561,12 @@
         <v>199</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="3">
-        <v>1</v>
-      </c>
-      <c r="B100" s="3">
-        <v>11</v>
+    <row r="100" spans="1:4" ht="28.8">
+      <c r="A100" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>106</v>
@@ -3455,12 +3575,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="3">
-        <v>1</v>
-      </c>
-      <c r="B101" s="3">
-        <v>11</v>
+    <row r="101" spans="1:4" ht="28.8">
+      <c r="A101" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>567</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>200</v>
@@ -3469,12 +3589,12 @@
         <v>201</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="3">
-        <v>1</v>
-      </c>
-      <c r="B102" s="3">
-        <v>12</v>
+    <row r="102" spans="1:4" ht="16.8">
+      <c r="A102" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>202</v>
@@ -3483,12 +3603,12 @@
         <v>203</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="3">
-        <v>1</v>
-      </c>
-      <c r="B103" s="3">
-        <v>12</v>
+    <row r="103" spans="1:4" ht="16.8">
+      <c r="A103" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>204</v>
@@ -3497,12 +3617,12 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="3">
-        <v>1</v>
-      </c>
-      <c r="B104" s="3">
-        <v>12</v>
+    <row r="104" spans="1:4" ht="16.8">
+      <c r="A104" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>206</v>
@@ -3511,12 +3631,12 @@
         <v>207</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="3">
-        <v>1</v>
-      </c>
-      <c r="B105" s="3">
-        <v>12</v>
+    <row r="105" spans="1:4" ht="16.8">
+      <c r="A105" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>208</v>
@@ -3525,12 +3645,12 @@
         <v>209</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="3">
-        <v>1</v>
-      </c>
-      <c r="B106" s="3">
-        <v>12</v>
+    <row r="106" spans="1:4" ht="16.8">
+      <c r="A106" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>210</v>
@@ -3539,12 +3659,12 @@
         <v>211</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="3">
-        <v>1</v>
-      </c>
-      <c r="B107" s="3">
-        <v>12</v>
+    <row r="107" spans="1:4" ht="16.8">
+      <c r="A107" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>212</v>
@@ -3553,12 +3673,12 @@
         <v>213</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="3">
-        <v>1</v>
-      </c>
-      <c r="B108" s="3">
-        <v>12</v>
+    <row r="108" spans="1:4" ht="16.8">
+      <c r="A108" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>214</v>
@@ -3567,12 +3687,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="3">
-        <v>1</v>
-      </c>
-      <c r="B109" s="3">
-        <v>12</v>
+    <row r="109" spans="1:4" ht="16.8">
+      <c r="A109" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>216</v>
@@ -3581,12 +3701,12 @@
         <v>217</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="3">
-        <v>1</v>
-      </c>
-      <c r="B110" s="3">
-        <v>12</v>
+    <row r="110" spans="1:4" ht="16.8">
+      <c r="A110" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>218</v>
@@ -3595,12 +3715,12 @@
         <v>219</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="3">
-        <v>1</v>
-      </c>
-      <c r="B111" s="3">
-        <v>12</v>
+    <row r="111" spans="1:4" ht="16.8">
+      <c r="A111" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>568</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>220</v>
@@ -3610,11 +3730,11 @@
       </c>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="3">
-        <v>1</v>
-      </c>
-      <c r="B112" s="3">
-        <v>13</v>
+      <c r="A112" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>222</v>
@@ -3624,11 +3744,11 @@
       </c>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="3">
-        <v>1</v>
-      </c>
-      <c r="B113" s="3">
-        <v>13</v>
+      <c r="A113" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>224</v>
@@ -3638,11 +3758,11 @@
       </c>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="3">
-        <v>1</v>
-      </c>
-      <c r="B114" s="3">
-        <v>13</v>
+      <c r="A114" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>226</v>
@@ -3652,11 +3772,11 @@
       </c>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="3">
-        <v>1</v>
-      </c>
-      <c r="B115" s="3">
-        <v>13</v>
+      <c r="A115" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>228</v>
@@ -3666,11 +3786,11 @@
       </c>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="3">
-        <v>1</v>
-      </c>
-      <c r="B116" s="3">
-        <v>13</v>
+      <c r="A116" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>230</v>
@@ -3680,11 +3800,11 @@
       </c>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="3">
-        <v>1</v>
-      </c>
-      <c r="B117" s="3">
-        <v>13</v>
+      <c r="A117" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>232</v>
@@ -3694,11 +3814,11 @@
       </c>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="3">
-        <v>1</v>
-      </c>
-      <c r="B118" s="3">
-        <v>13</v>
+      <c r="A118" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>234</v>
@@ -3708,11 +3828,11 @@
       </c>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="3">
-        <v>1</v>
-      </c>
-      <c r="B119" s="3">
-        <v>13</v>
+      <c r="A119" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>236</v>
@@ -3722,11 +3842,11 @@
       </c>
     </row>
     <row r="120" spans="1:4">
-      <c r="A120" s="3">
-        <v>1</v>
-      </c>
-      <c r="B120" s="3">
-        <v>13</v>
+      <c r="A120" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>238</v>
@@ -3736,11 +3856,11 @@
       </c>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="3">
-        <v>1</v>
-      </c>
-      <c r="B121" s="3">
-        <v>13</v>
+      <c r="A121" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>569</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>240</v>
@@ -3750,11 +3870,11 @@
       </c>
     </row>
     <row r="122" spans="1:4" ht="30">
-      <c r="A122" s="3">
-        <v>1</v>
-      </c>
-      <c r="B122" s="3">
-        <v>14</v>
+      <c r="A122" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>242</v>
@@ -3763,12 +3883,12 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
-      <c r="A123" s="3">
-        <v>1</v>
-      </c>
-      <c r="B123" s="3">
-        <v>14</v>
+    <row r="123" spans="1:4" ht="16.8">
+      <c r="A123" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>244</v>
@@ -3777,12 +3897,12 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
-      <c r="A124" s="3">
-        <v>1</v>
-      </c>
-      <c r="B124" s="3">
-        <v>14</v>
+    <row r="124" spans="1:4" ht="16.8">
+      <c r="A124" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>246</v>
@@ -3791,12 +3911,12 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
-      <c r="A125" s="3">
-        <v>1</v>
-      </c>
-      <c r="B125" s="3">
-        <v>14</v>
+    <row r="125" spans="1:4" ht="16.8">
+      <c r="A125" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>248</v>
@@ -3805,12 +3925,12 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
-      <c r="A126" s="3">
-        <v>1</v>
-      </c>
-      <c r="B126" s="3">
-        <v>14</v>
+    <row r="126" spans="1:4" ht="16.8">
+      <c r="A126" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>250</v>
@@ -3819,12 +3939,12 @@
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
-      <c r="A127" s="3">
-        <v>1</v>
-      </c>
-      <c r="B127" s="3">
-        <v>14</v>
+    <row r="127" spans="1:4" ht="16.8">
+      <c r="A127" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>252</v>
@@ -3833,12 +3953,12 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
-      <c r="A128" s="3">
-        <v>1</v>
-      </c>
-      <c r="B128" s="3">
-        <v>14</v>
+    <row r="128" spans="1:4" ht="16.8">
+      <c r="A128" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>254</v>
@@ -3847,12 +3967,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="3">
-        <v>1</v>
-      </c>
-      <c r="B129" s="3">
-        <v>14</v>
+    <row r="129" spans="1:4" ht="16.8">
+      <c r="A129" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>256</v>
@@ -3862,11 +3982,11 @@
       </c>
     </row>
     <row r="130" spans="1:4" ht="30">
-      <c r="A130" s="3">
-        <v>1</v>
-      </c>
-      <c r="B130" s="3">
-        <v>14</v>
+      <c r="A130" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>258</v>
@@ -3875,12 +3995,12 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
-      <c r="A131" s="3">
-        <v>1</v>
-      </c>
-      <c r="B131" s="3">
-        <v>14</v>
+    <row r="131" spans="1:4" ht="16.8">
+      <c r="A131" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>570</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>260</v>
@@ -3889,12 +4009,12 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="3">
-        <v>1</v>
-      </c>
-      <c r="B132" s="3">
-        <v>15</v>
+    <row r="132" spans="1:4" ht="28.8">
+      <c r="A132" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>262</v>
@@ -3903,12 +4023,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
-      <c r="A133" s="3">
-        <v>1</v>
-      </c>
-      <c r="B133" s="3">
-        <v>15</v>
+    <row r="133" spans="1:4" ht="28.8">
+      <c r="A133" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>264</v>
@@ -3917,12 +4037,12 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
-      <c r="A134" s="3">
-        <v>1</v>
-      </c>
-      <c r="B134" s="3">
-        <v>15</v>
+    <row r="134" spans="1:4" ht="28.8">
+      <c r="A134" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>266</v>
@@ -3931,12 +4051,12 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
-      <c r="A135" s="3">
-        <v>1</v>
-      </c>
-      <c r="B135" s="3">
-        <v>15</v>
+    <row r="135" spans="1:4" ht="28.8">
+      <c r="A135" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>268</v>
@@ -3945,12 +4065,12 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="3">
-        <v>1</v>
-      </c>
-      <c r="B136" s="3">
-        <v>15</v>
+    <row r="136" spans="1:4" ht="28.8">
+      <c r="A136" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>270</v>
@@ -3959,12 +4079,12 @@
         <v>271</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
-      <c r="A137" s="3">
-        <v>1</v>
-      </c>
-      <c r="B137" s="3">
-        <v>15</v>
+    <row r="137" spans="1:4" ht="28.8">
+      <c r="A137" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>272</v>
@@ -3973,12 +4093,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
-      <c r="A138" s="3">
-        <v>1</v>
-      </c>
-      <c r="B138" s="3">
-        <v>15</v>
+    <row r="138" spans="1:4" ht="28.8">
+      <c r="A138" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>274</v>
@@ -3987,12 +4107,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
-      <c r="A139" s="3">
-        <v>1</v>
-      </c>
-      <c r="B139" s="3">
-        <v>15</v>
+    <row r="139" spans="1:4" ht="28.8">
+      <c r="A139" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>276</v>
@@ -4001,12 +4121,12 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
-      <c r="A140" s="3">
-        <v>1</v>
-      </c>
-      <c r="B140" s="3">
-        <v>15</v>
+    <row r="140" spans="1:4" ht="28.8">
+      <c r="A140" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>278</v>
@@ -4015,12 +4135,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
-      <c r="A141" s="3">
-        <v>1</v>
-      </c>
-      <c r="B141" s="3">
-        <v>15</v>
+    <row r="141" spans="1:4" ht="28.8">
+      <c r="A141" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>571</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>280</v>
@@ -4029,12 +4149,12 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="3">
-        <v>1</v>
-      </c>
-      <c r="B142" s="3">
-        <v>16</v>
+    <row r="142" spans="1:4" ht="16.8">
+      <c r="A142" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>282</v>
@@ -4043,12 +4163,12 @@
         <v>283</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
-      <c r="A143" s="3">
-        <v>1</v>
-      </c>
-      <c r="B143" s="3">
-        <v>16</v>
+    <row r="143" spans="1:4" ht="16.8">
+      <c r="A143" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>284</v>
@@ -4057,12 +4177,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
-      <c r="A144" s="3">
-        <v>1</v>
-      </c>
-      <c r="B144" s="3">
-        <v>16</v>
+    <row r="144" spans="1:4" ht="16.8">
+      <c r="A144" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>286</v>
@@ -4071,12 +4191,12 @@
         <v>287</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
-      <c r="A145" s="3">
-        <v>1</v>
-      </c>
-      <c r="B145" s="3">
-        <v>16</v>
+    <row r="145" spans="1:4" ht="16.8">
+      <c r="A145" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>288</v>
@@ -4085,12 +4205,12 @@
         <v>289</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
-      <c r="A146" s="3">
-        <v>1</v>
-      </c>
-      <c r="B146" s="3">
-        <v>16</v>
+    <row r="146" spans="1:4" ht="16.8">
+      <c r="A146" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>290</v>
@@ -4099,12 +4219,12 @@
         <v>291</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
-      <c r="A147" s="3">
-        <v>1</v>
-      </c>
-      <c r="B147" s="3">
-        <v>16</v>
+    <row r="147" spans="1:4" ht="16.8">
+      <c r="A147" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>292</v>
@@ -4113,12 +4233,12 @@
         <v>293</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
-      <c r="A148" s="3">
-        <v>1</v>
-      </c>
-      <c r="B148" s="3">
-        <v>16</v>
+    <row r="148" spans="1:4" ht="16.8">
+      <c r="A148" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>294</v>
@@ -4127,12 +4247,12 @@
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
-      <c r="A149" s="3">
-        <v>1</v>
-      </c>
-      <c r="B149" s="3">
-        <v>16</v>
+    <row r="149" spans="1:4" ht="16.8">
+      <c r="A149" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>296</v>
@@ -4141,12 +4261,12 @@
         <v>297</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
-      <c r="A150" s="3">
-        <v>1</v>
-      </c>
-      <c r="B150" s="3">
-        <v>16</v>
+    <row r="150" spans="1:4" ht="16.8">
+      <c r="A150" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>298</v>
@@ -4155,12 +4275,12 @@
         <v>299</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
-      <c r="A151" s="3">
-        <v>1</v>
-      </c>
-      <c r="B151" s="3">
-        <v>16</v>
+    <row r="151" spans="1:4" ht="16.8">
+      <c r="A151" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>572</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>300</v>
@@ -4169,12 +4289,12 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="3">
-        <v>1</v>
-      </c>
-      <c r="B152" s="3">
-        <v>17</v>
+    <row r="152" spans="1:4" ht="16.8">
+      <c r="A152" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>302</v>
@@ -4183,12 +4303,12 @@
         <v>303</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
-      <c r="A153" s="3">
-        <v>1</v>
-      </c>
-      <c r="B153" s="3">
-        <v>17</v>
+    <row r="153" spans="1:4" ht="16.8">
+      <c r="A153" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>304</v>
@@ -4198,11 +4318,11 @@
       </c>
     </row>
     <row r="154" spans="1:4" ht="30">
-      <c r="A154" s="3">
-        <v>1</v>
-      </c>
-      <c r="B154" s="3">
-        <v>17</v>
+      <c r="A154" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>306</v>
@@ -4211,12 +4331,12 @@
         <v>307</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
-      <c r="A155" s="3">
-        <v>1</v>
-      </c>
-      <c r="B155" s="3">
-        <v>17</v>
+    <row r="155" spans="1:4" ht="16.8">
+      <c r="A155" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>308</v>
@@ -4225,12 +4345,12 @@
         <v>309</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
-      <c r="A156" s="3">
-        <v>1</v>
-      </c>
-      <c r="B156" s="3">
-        <v>17</v>
+    <row r="156" spans="1:4" ht="16.8">
+      <c r="A156" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>310</v>
@@ -4239,12 +4359,12 @@
         <v>311</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
-      <c r="A157" s="3">
-        <v>1</v>
-      </c>
-      <c r="B157" s="3">
-        <v>17</v>
+    <row r="157" spans="1:4" ht="16.8">
+      <c r="A157" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>312</v>
@@ -4253,12 +4373,12 @@
         <v>313</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
-      <c r="A158" s="3">
-        <v>1</v>
-      </c>
-      <c r="B158" s="3">
-        <v>17</v>
+    <row r="158" spans="1:4" ht="16.8">
+      <c r="A158" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>314</v>
@@ -4267,12 +4387,12 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
-      <c r="A159" s="3">
-        <v>1</v>
-      </c>
-      <c r="B159" s="3">
-        <v>17</v>
+    <row r="159" spans="1:4" ht="16.8">
+      <c r="A159" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>316</v>
@@ -4281,12 +4401,12 @@
         <v>317</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
-      <c r="A160" s="3">
-        <v>1</v>
-      </c>
-      <c r="B160" s="3">
-        <v>17</v>
+    <row r="160" spans="1:4" ht="16.8">
+      <c r="A160" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>318</v>
@@ -4295,12 +4415,12 @@
         <v>319</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
-      <c r="A161" s="3">
-        <v>1</v>
-      </c>
-      <c r="B161" s="3">
-        <v>17</v>
+    <row r="161" spans="1:4" ht="16.8">
+      <c r="A161" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>573</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>320</v>
@@ -4310,11 +4430,11 @@
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="3">
-        <v>1</v>
-      </c>
-      <c r="B162" s="3">
-        <v>18</v>
+      <c r="A162" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>322</v>
@@ -4324,11 +4444,11 @@
       </c>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="3">
-        <v>1</v>
-      </c>
-      <c r="B163" s="3">
-        <v>18</v>
+      <c r="A163" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>324</v>
@@ -4338,11 +4458,11 @@
       </c>
     </row>
     <row r="164" spans="1:4">
-      <c r="A164" s="3">
-        <v>1</v>
-      </c>
-      <c r="B164" s="3">
-        <v>18</v>
+      <c r="A164" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>326</v>
@@ -4352,11 +4472,11 @@
       </c>
     </row>
     <row r="165" spans="1:4">
-      <c r="A165" s="3">
-        <v>1</v>
-      </c>
-      <c r="B165" s="3">
-        <v>18</v>
+      <c r="A165" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>328</v>
@@ -4366,11 +4486,11 @@
       </c>
     </row>
     <row r="166" spans="1:4">
-      <c r="A166" s="3">
-        <v>1</v>
-      </c>
-      <c r="B166" s="3">
-        <v>18</v>
+      <c r="A166" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>330</v>
@@ -4380,11 +4500,11 @@
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="3">
-        <v>1</v>
-      </c>
-      <c r="B167" s="3">
-        <v>18</v>
+      <c r="A167" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>332</v>
@@ -4394,11 +4514,11 @@
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="3">
-        <v>1</v>
-      </c>
-      <c r="B168" s="3">
-        <v>18</v>
+      <c r="A168" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>334</v>
@@ -4408,11 +4528,11 @@
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="3">
-        <v>1</v>
-      </c>
-      <c r="B169" s="3">
-        <v>18</v>
+      <c r="A169" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>336</v>
@@ -4422,11 +4542,11 @@
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="3">
-        <v>1</v>
-      </c>
-      <c r="B170" s="3">
-        <v>18</v>
+      <c r="A170" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>338</v>
@@ -4436,11 +4556,11 @@
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="3">
-        <v>1</v>
-      </c>
-      <c r="B171" s="3">
-        <v>18</v>
+      <c r="A171" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>340</v>
@@ -4449,12 +4569,12 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
-      <c r="A172" s="3">
-        <v>1</v>
-      </c>
-      <c r="B172" s="3">
-        <v>19</v>
+    <row r="172" spans="1:4" ht="16.8">
+      <c r="A172" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>342</v>
@@ -4463,12 +4583,12 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
-      <c r="A173" s="3">
-        <v>1</v>
-      </c>
-      <c r="B173" s="3">
-        <v>19</v>
+    <row r="173" spans="1:4" ht="16.8">
+      <c r="A173" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>344</v>
@@ -4477,12 +4597,12 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
-      <c r="A174" s="3">
-        <v>1</v>
-      </c>
-      <c r="B174" s="3">
-        <v>19</v>
+    <row r="174" spans="1:4" ht="16.8">
+      <c r="A174" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>346</v>
@@ -4491,12 +4611,12 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
-      <c r="A175" s="3">
-        <v>1</v>
-      </c>
-      <c r="B175" s="3">
-        <v>19</v>
+    <row r="175" spans="1:4" ht="16.8">
+      <c r="A175" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>348</v>
@@ -4505,12 +4625,12 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
-      <c r="A176" s="3">
-        <v>1</v>
-      </c>
-      <c r="B176" s="3">
-        <v>19</v>
+    <row r="176" spans="1:4" ht="16.8">
+      <c r="A176" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>350</v>
@@ -4519,12 +4639,12 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" spans="1:4">
-      <c r="A177" s="3">
-        <v>1</v>
-      </c>
-      <c r="B177" s="3">
-        <v>19</v>
+    <row r="177" spans="1:4" ht="16.8">
+      <c r="A177" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>352</v>
@@ -4533,12 +4653,12 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
-      <c r="A178" s="3">
-        <v>1</v>
-      </c>
-      <c r="B178" s="3">
-        <v>19</v>
+    <row r="178" spans="1:4" ht="16.8">
+      <c r="A178" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>354</v>
@@ -4547,12 +4667,12 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
-      <c r="A179" s="3">
-        <v>1</v>
-      </c>
-      <c r="B179" s="3">
-        <v>19</v>
+    <row r="179" spans="1:4" ht="16.8">
+      <c r="A179" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>356</v>
@@ -4561,12 +4681,12 @@
         <v>357</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
-      <c r="A180" s="3">
-        <v>1</v>
-      </c>
-      <c r="B180" s="3">
-        <v>19</v>
+    <row r="180" spans="1:4" ht="16.8">
+      <c r="A180" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>358</v>
@@ -4575,12 +4695,12 @@
         <v>359</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
-      <c r="A181" s="3">
-        <v>1</v>
-      </c>
-      <c r="B181" s="3">
-        <v>19</v>
+    <row r="181" spans="1:4" ht="16.8">
+      <c r="A181" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>575</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>344</v>
@@ -4589,12 +4709,12 @@
         <v>345</v>
       </c>
     </row>
-    <row r="182" spans="1:4">
-      <c r="A182" s="3">
-        <v>1</v>
-      </c>
-      <c r="B182" s="3">
-        <v>20</v>
+    <row r="182" spans="1:4" ht="16.8">
+      <c r="A182" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>360</v>
@@ -4603,12 +4723,12 @@
         <v>361</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
-      <c r="A183" s="3">
-        <v>1</v>
-      </c>
-      <c r="B183" s="3">
-        <v>20</v>
+    <row r="183" spans="1:4" ht="16.8">
+      <c r="A183" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>362</v>
@@ -4617,12 +4737,12 @@
         <v>363</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
-      <c r="A184" s="3">
-        <v>1</v>
-      </c>
-      <c r="B184" s="3">
-        <v>20</v>
+    <row r="184" spans="1:4" ht="16.8">
+      <c r="A184" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>364</v>
@@ -4631,12 +4751,12 @@
         <v>365</v>
       </c>
     </row>
-    <row r="185" spans="1:4">
-      <c r="A185" s="3">
-        <v>1</v>
-      </c>
-      <c r="B185" s="3">
-        <v>20</v>
+    <row r="185" spans="1:4" ht="16.8">
+      <c r="A185" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>366</v>
@@ -4645,12 +4765,12 @@
         <v>367</v>
       </c>
     </row>
-    <row r="186" spans="1:4">
-      <c r="A186" s="3">
-        <v>1</v>
-      </c>
-      <c r="B186" s="3">
-        <v>20</v>
+    <row r="186" spans="1:4" ht="16.8">
+      <c r="A186" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>368</v>
@@ -4659,12 +4779,12 @@
         <v>369</v>
       </c>
     </row>
-    <row r="187" spans="1:4">
-      <c r="A187" s="3">
-        <v>1</v>
-      </c>
-      <c r="B187" s="3">
-        <v>20</v>
+    <row r="187" spans="1:4" ht="16.8">
+      <c r="A187" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>370</v>
@@ -4673,12 +4793,12 @@
         <v>371</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
-      <c r="A188" s="3">
-        <v>1</v>
-      </c>
-      <c r="B188" s="3">
-        <v>20</v>
+    <row r="188" spans="1:4" ht="16.8">
+      <c r="A188" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>372</v>
@@ -4687,12 +4807,12 @@
         <v>373</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
-      <c r="A189" s="3">
-        <v>1</v>
-      </c>
-      <c r="B189" s="3">
-        <v>20</v>
+    <row r="189" spans="1:4" ht="16.8">
+      <c r="A189" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>374</v>
@@ -4701,12 +4821,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="190" spans="1:4">
-      <c r="A190" s="3">
-        <v>1</v>
-      </c>
-      <c r="B190" s="3">
-        <v>20</v>
+    <row r="190" spans="1:4" ht="16.8">
+      <c r="A190" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>376</v>
@@ -4715,12 +4835,12 @@
         <v>377</v>
       </c>
     </row>
-    <row r="191" spans="1:4">
-      <c r="A191" s="3">
-        <v>1</v>
-      </c>
-      <c r="B191" s="3">
-        <v>20</v>
+    <row r="191" spans="1:4" ht="16.8">
+      <c r="A191" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>577</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>378</v>
@@ -4729,12 +4849,12 @@
         <v>379</v>
       </c>
     </row>
-    <row r="192" spans="1:4">
-      <c r="A192" s="3">
-        <v>1</v>
-      </c>
-      <c r="B192" s="3">
-        <v>21</v>
+    <row r="192" spans="1:4" ht="16.8">
+      <c r="A192" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>380</v>
@@ -4743,12 +4863,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
-      <c r="A193" s="3">
-        <v>1</v>
-      </c>
-      <c r="B193" s="3">
-        <v>21</v>
+    <row r="193" spans="1:4" ht="16.8">
+      <c r="A193" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>382</v>
@@ -4757,12 +4877,12 @@
         <v>383</v>
       </c>
     </row>
-    <row r="194" spans="1:4">
-      <c r="A194" s="3">
-        <v>1</v>
-      </c>
-      <c r="B194" s="3">
-        <v>21</v>
+    <row r="194" spans="1:4" ht="16.8">
+      <c r="A194" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>384</v>
@@ -4771,12 +4891,12 @@
         <v>385</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
-      <c r="A195" s="3">
-        <v>1</v>
-      </c>
-      <c r="B195" s="3">
-        <v>21</v>
+    <row r="195" spans="1:4" ht="16.8">
+      <c r="A195" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>386</v>
@@ -4785,12 +4905,12 @@
         <v>387</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
-      <c r="A196" s="3">
-        <v>1</v>
-      </c>
-      <c r="B196" s="3">
-        <v>21</v>
+    <row r="196" spans="1:4" ht="16.8">
+      <c r="A196" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>388</v>
@@ -4799,12 +4919,12 @@
         <v>389</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
-      <c r="A197" s="3">
-        <v>1</v>
-      </c>
-      <c r="B197" s="3">
-        <v>21</v>
+    <row r="197" spans="1:4" ht="16.8">
+      <c r="A197" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B197" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>390</v>
@@ -4813,12 +4933,12 @@
         <v>391</v>
       </c>
     </row>
-    <row r="198" spans="1:4">
-      <c r="A198" s="3">
-        <v>1</v>
-      </c>
-      <c r="B198" s="3">
-        <v>21</v>
+    <row r="198" spans="1:4" ht="16.8">
+      <c r="A198" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B198" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>392</v>
@@ -4827,12 +4947,12 @@
         <v>393</v>
       </c>
     </row>
-    <row r="199" spans="1:4">
-      <c r="A199" s="3">
-        <v>1</v>
-      </c>
-      <c r="B199" s="3">
-        <v>21</v>
+    <row r="199" spans="1:4" ht="16.8">
+      <c r="A199" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>394</v>
@@ -4841,12 +4961,12 @@
         <v>395</v>
       </c>
     </row>
-    <row r="200" spans="1:4">
-      <c r="A200" s="3">
-        <v>1</v>
-      </c>
-      <c r="B200" s="3">
-        <v>21</v>
+    <row r="200" spans="1:4" ht="16.8">
+      <c r="A200" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>396</v>
@@ -4855,12 +4975,12 @@
         <v>397</v>
       </c>
     </row>
-    <row r="201" spans="1:4">
-      <c r="A201" s="3">
-        <v>1</v>
-      </c>
-      <c r="B201" s="3">
-        <v>21</v>
+    <row r="201" spans="1:4" ht="16.8">
+      <c r="A201" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>578</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>398</v>
@@ -4869,12 +4989,12 @@
         <v>399</v>
       </c>
     </row>
-    <row r="202" spans="1:4">
-      <c r="A202" s="3">
-        <v>1</v>
-      </c>
-      <c r="B202" s="3">
-        <v>22</v>
+    <row r="202" spans="1:4" ht="16.8">
+      <c r="A202" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>164</v>
@@ -4883,12 +5003,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
-      <c r="A203" s="3">
-        <v>1</v>
-      </c>
-      <c r="B203" s="3">
-        <v>22</v>
+    <row r="203" spans="1:4" ht="16.8">
+      <c r="A203" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>400</v>
@@ -4897,12 +5017,12 @@
         <v>401</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
-      <c r="A204" s="3">
-        <v>1</v>
-      </c>
-      <c r="B204" s="3">
-        <v>22</v>
+    <row r="204" spans="1:4" ht="16.8">
+      <c r="A204" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>402</v>
@@ -4911,12 +5031,12 @@
         <v>403</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
-      <c r="A205" s="3">
-        <v>1</v>
-      </c>
-      <c r="B205" s="3">
-        <v>22</v>
+    <row r="205" spans="1:4" ht="16.8">
+      <c r="A205" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>404</v>
@@ -4925,12 +5045,12 @@
         <v>405</v>
       </c>
     </row>
-    <row r="206" spans="1:4">
-      <c r="A206" s="3">
-        <v>1</v>
-      </c>
-      <c r="B206" s="3">
-        <v>22</v>
+    <row r="206" spans="1:4" ht="16.8">
+      <c r="A206" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>406</v>
@@ -4939,12 +5059,12 @@
         <v>407</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
-      <c r="A207" s="3">
-        <v>1</v>
-      </c>
-      <c r="B207" s="3">
-        <v>22</v>
+    <row r="207" spans="1:4" ht="16.8">
+      <c r="A207" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>408</v>
@@ -4953,12 +5073,12 @@
         <v>409</v>
       </c>
     </row>
-    <row r="208" spans="1:4">
-      <c r="A208" s="3">
-        <v>1</v>
-      </c>
-      <c r="B208" s="3">
-        <v>22</v>
+    <row r="208" spans="1:4" ht="16.8">
+      <c r="A208" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>410</v>
@@ -4967,12 +5087,12 @@
         <v>411</v>
       </c>
     </row>
-    <row r="209" spans="1:4">
-      <c r="A209" s="3">
-        <v>1</v>
-      </c>
-      <c r="B209" s="3">
-        <v>22</v>
+    <row r="209" spans="1:4" ht="16.8">
+      <c r="A209" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>412</v>
@@ -4981,12 +5101,12 @@
         <v>413</v>
       </c>
     </row>
-    <row r="210" spans="1:4">
-      <c r="A210" s="3">
-        <v>1</v>
-      </c>
-      <c r="B210" s="3">
-        <v>22</v>
+    <row r="210" spans="1:4" ht="16.8">
+      <c r="A210" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>414</v>
@@ -4995,12 +5115,12 @@
         <v>415</v>
       </c>
     </row>
-    <row r="211" spans="1:4">
-      <c r="A211" s="3">
-        <v>1</v>
-      </c>
-      <c r="B211" s="3">
-        <v>22</v>
+    <row r="211" spans="1:4" ht="16.8">
+      <c r="A211" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>416</v>
@@ -5009,12 +5129,12 @@
         <v>417</v>
       </c>
     </row>
-    <row r="212" spans="1:4">
-      <c r="A212" s="3">
-        <v>1</v>
-      </c>
-      <c r="B212" s="3">
-        <v>23</v>
+    <row r="212" spans="1:4" ht="16.8">
+      <c r="A212" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>418</v>
@@ -5023,12 +5143,12 @@
         <v>419</v>
       </c>
     </row>
-    <row r="213" spans="1:4">
-      <c r="A213" s="3">
-        <v>1</v>
-      </c>
-      <c r="B213" s="3">
-        <v>23</v>
+    <row r="213" spans="1:4" ht="16.8">
+      <c r="A213" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>420</v>
@@ -5037,12 +5157,12 @@
         <v>421</v>
       </c>
     </row>
-    <row r="214" spans="1:4">
-      <c r="A214" s="3">
-        <v>1</v>
-      </c>
-      <c r="B214" s="3">
-        <v>23</v>
+    <row r="214" spans="1:4" ht="16.8">
+      <c r="A214" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>422</v>
@@ -5051,12 +5171,12 @@
         <v>423</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
-      <c r="A215" s="3">
-        <v>1</v>
-      </c>
-      <c r="B215" s="3">
-        <v>23</v>
+    <row r="215" spans="1:4" ht="16.8">
+      <c r="A215" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>424</v>
@@ -5065,12 +5185,12 @@
         <v>425</v>
       </c>
     </row>
-    <row r="216" spans="1:4">
-      <c r="A216" s="3">
-        <v>1</v>
-      </c>
-      <c r="B216" s="3">
-        <v>23</v>
+    <row r="216" spans="1:4" ht="16.8">
+      <c r="A216" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>426</v>
@@ -5079,12 +5199,12 @@
         <v>427</v>
       </c>
     </row>
-    <row r="217" spans="1:4">
-      <c r="A217" s="3">
-        <v>1</v>
-      </c>
-      <c r="B217" s="3">
-        <v>23</v>
+    <row r="217" spans="1:4" ht="16.8">
+      <c r="A217" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>428</v>
@@ -5093,12 +5213,12 @@
         <v>429</v>
       </c>
     </row>
-    <row r="218" spans="1:4">
-      <c r="A218" s="3">
-        <v>1</v>
-      </c>
-      <c r="B218" s="3">
-        <v>23</v>
+    <row r="218" spans="1:4" ht="16.8">
+      <c r="A218" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>430</v>
@@ -5107,12 +5227,12 @@
         <v>431</v>
       </c>
     </row>
-    <row r="219" spans="1:4">
-      <c r="A219" s="3">
-        <v>1</v>
-      </c>
-      <c r="B219" s="3">
-        <v>23</v>
+    <row r="219" spans="1:4" ht="16.8">
+      <c r="A219" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>432</v>
@@ -5121,12 +5241,12 @@
         <v>433</v>
       </c>
     </row>
-    <row r="220" spans="1:4">
-      <c r="A220" s="3">
-        <v>1</v>
-      </c>
-      <c r="B220" s="3">
-        <v>23</v>
+    <row r="220" spans="1:4" ht="16.8">
+      <c r="A220" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>434</v>
@@ -5135,12 +5255,12 @@
         <v>435</v>
       </c>
     </row>
-    <row r="221" spans="1:4">
-      <c r="A221" s="3">
-        <v>1</v>
-      </c>
-      <c r="B221" s="3">
-        <v>23</v>
+    <row r="221" spans="1:4" ht="16.8">
+      <c r="A221" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>580</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>436</v>
@@ -5149,12 +5269,12 @@
         <v>437</v>
       </c>
     </row>
-    <row r="222" spans="1:4">
-      <c r="A222" s="3">
-        <v>1</v>
-      </c>
-      <c r="B222" s="3">
-        <v>24</v>
+    <row r="222" spans="1:4" ht="16.8">
+      <c r="A222" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>438</v>
@@ -5163,12 +5283,12 @@
         <v>439</v>
       </c>
     </row>
-    <row r="223" spans="1:4">
-      <c r="A223" s="3">
-        <v>1</v>
-      </c>
-      <c r="B223" s="3">
-        <v>24</v>
+    <row r="223" spans="1:4" ht="16.8">
+      <c r="A223" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>440</v>
@@ -5177,12 +5297,12 @@
         <v>441</v>
       </c>
     </row>
-    <row r="224" spans="1:4">
-      <c r="A224" s="3">
-        <v>1</v>
-      </c>
-      <c r="B224" s="3">
-        <v>24</v>
+    <row r="224" spans="1:4" ht="16.8">
+      <c r="A224" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>442</v>
@@ -5191,12 +5311,12 @@
         <v>443</v>
       </c>
     </row>
-    <row r="225" spans="1:4">
-      <c r="A225" s="3">
-        <v>1</v>
-      </c>
-      <c r="B225" s="3">
-        <v>24</v>
+    <row r="225" spans="1:4" ht="16.8">
+      <c r="A225" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>444</v>
@@ -5205,12 +5325,12 @@
         <v>445</v>
       </c>
     </row>
-    <row r="226" spans="1:4">
-      <c r="A226" s="3">
-        <v>1</v>
-      </c>
-      <c r="B226" s="3">
-        <v>24</v>
+    <row r="226" spans="1:4" ht="16.8">
+      <c r="A226" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>446</v>
@@ -5219,12 +5339,12 @@
         <v>447</v>
       </c>
     </row>
-    <row r="227" spans="1:4">
-      <c r="A227" s="3">
-        <v>1</v>
-      </c>
-      <c r="B227" s="3">
-        <v>24</v>
+    <row r="227" spans="1:4" ht="16.8">
+      <c r="A227" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>448</v>
@@ -5233,12 +5353,12 @@
         <v>449</v>
       </c>
     </row>
-    <row r="228" spans="1:4">
-      <c r="A228" s="3">
-        <v>1</v>
-      </c>
-      <c r="B228" s="3">
-        <v>24</v>
+    <row r="228" spans="1:4" ht="16.8">
+      <c r="A228" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>450</v>
@@ -5247,12 +5367,12 @@
         <v>451</v>
       </c>
     </row>
-    <row r="229" spans="1:4">
-      <c r="A229" s="3">
-        <v>1</v>
-      </c>
-      <c r="B229" s="3">
-        <v>24</v>
+    <row r="229" spans="1:4" ht="16.8">
+      <c r="A229" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>452</v>
@@ -5261,12 +5381,12 @@
         <v>453</v>
       </c>
     </row>
-    <row r="230" spans="1:4">
-      <c r="A230" s="3">
-        <v>1</v>
-      </c>
-      <c r="B230" s="3">
-        <v>24</v>
+    <row r="230" spans="1:4" ht="16.8">
+      <c r="A230" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>454</v>
@@ -5275,12 +5395,12 @@
         <v>455</v>
       </c>
     </row>
-    <row r="231" spans="1:4">
-      <c r="A231" s="3">
-        <v>1</v>
-      </c>
-      <c r="B231" s="3">
-        <v>24</v>
+    <row r="231" spans="1:4" ht="16.8">
+      <c r="A231" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>581</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>456</v>
@@ -5290,11 +5410,11 @@
       </c>
     </row>
     <row r="232" spans="1:4">
-      <c r="A232" s="3">
-        <v>1</v>
-      </c>
-      <c r="B232" s="3">
-        <v>25</v>
+      <c r="A232" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>458</v>
@@ -5304,11 +5424,11 @@
       </c>
     </row>
     <row r="233" spans="1:4">
-      <c r="A233" s="3">
-        <v>1</v>
-      </c>
-      <c r="B233" s="3">
-        <v>25</v>
+      <c r="A233" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>460</v>
@@ -5318,11 +5438,11 @@
       </c>
     </row>
     <row r="234" spans="1:4">
-      <c r="A234" s="3">
-        <v>1</v>
-      </c>
-      <c r="B234" s="3">
-        <v>25</v>
+      <c r="A234" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>462</v>
@@ -5331,12 +5451,12 @@
         <v>463</v>
       </c>
     </row>
-    <row r="235" spans="1:4" ht="30">
-      <c r="A235" s="3">
-        <v>1</v>
-      </c>
-      <c r="B235" s="3">
-        <v>25</v>
+    <row r="235" spans="1:4">
+      <c r="A235" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>464</v>
@@ -5346,11 +5466,11 @@
       </c>
     </row>
     <row r="236" spans="1:4">
-      <c r="A236" s="3">
-        <v>1</v>
-      </c>
-      <c r="B236" s="3">
-        <v>25</v>
+      <c r="A236" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>466</v>
@@ -5360,11 +5480,11 @@
       </c>
     </row>
     <row r="237" spans="1:4">
-      <c r="A237" s="3">
-        <v>1</v>
-      </c>
-      <c r="B237" s="3">
-        <v>25</v>
+      <c r="A237" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>468</v>
@@ -5374,11 +5494,11 @@
       </c>
     </row>
     <row r="238" spans="1:4">
-      <c r="A238" s="3">
-        <v>1</v>
-      </c>
-      <c r="B238" s="3">
-        <v>25</v>
+      <c r="A238" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>470</v>
@@ -5388,11 +5508,11 @@
       </c>
     </row>
     <row r="239" spans="1:4">
-      <c r="A239" s="3">
-        <v>1</v>
-      </c>
-      <c r="B239" s="3">
-        <v>25</v>
+      <c r="A239" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>472</v>
@@ -5402,11 +5522,11 @@
       </c>
     </row>
     <row r="240" spans="1:4">
-      <c r="A240" s="3">
-        <v>1</v>
-      </c>
-      <c r="B240" s="3">
-        <v>25</v>
+      <c r="A240" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>474</v>
@@ -5416,11 +5536,11 @@
       </c>
     </row>
     <row r="241" spans="1:4">
-      <c r="A241" s="3">
-        <v>1</v>
-      </c>
-      <c r="B241" s="3">
-        <v>25</v>
+      <c r="A241" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>582</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>476</v>
@@ -5429,12 +5549,12 @@
         <v>477</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
-      <c r="A242" s="3">
-        <v>1</v>
-      </c>
-      <c r="B242" s="3">
-        <v>26</v>
+    <row r="242" spans="1:4" ht="16.8">
+      <c r="A242" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>478</v>
@@ -5443,12 +5563,12 @@
         <v>479</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
-      <c r="A243" s="3">
-        <v>1</v>
-      </c>
-      <c r="B243" s="3">
-        <v>26</v>
+    <row r="243" spans="1:4" ht="16.8">
+      <c r="A243" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>480</v>
@@ -5457,12 +5577,12 @@
         <v>481</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
-      <c r="A244" s="3">
-        <v>1</v>
-      </c>
-      <c r="B244" s="3">
-        <v>26</v>
+    <row r="244" spans="1:4" ht="16.8">
+      <c r="A244" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>482</v>
@@ -5471,12 +5591,12 @@
         <v>483</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
-      <c r="A245" s="3">
-        <v>1</v>
-      </c>
-      <c r="B245" s="3">
-        <v>26</v>
+    <row r="245" spans="1:4" ht="16.8">
+      <c r="A245" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>484</v>
@@ -5485,12 +5605,12 @@
         <v>485</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
-      <c r="A246" s="3">
-        <v>1</v>
-      </c>
-      <c r="B246" s="3">
-        <v>26</v>
+    <row r="246" spans="1:4" ht="16.8">
+      <c r="A246" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>486</v>
@@ -5499,12 +5619,12 @@
         <v>487</v>
       </c>
     </row>
-    <row r="247" spans="1:4" ht="30">
-      <c r="A247" s="3">
-        <v>1</v>
-      </c>
-      <c r="B247" s="3">
-        <v>26</v>
+    <row r="247" spans="1:4" ht="16.8">
+      <c r="A247" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>488</v>
@@ -5513,12 +5633,12 @@
         <v>489</v>
       </c>
     </row>
-    <row r="248" spans="1:4">
-      <c r="A248" s="3">
-        <v>1</v>
-      </c>
-      <c r="B248" s="3">
-        <v>26</v>
+    <row r="248" spans="1:4" ht="16.8">
+      <c r="A248" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>490</v>
@@ -5527,12 +5647,12 @@
         <v>491</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
-      <c r="A249" s="3">
-        <v>1</v>
-      </c>
-      <c r="B249" s="3">
-        <v>26</v>
+    <row r="249" spans="1:4" ht="16.8">
+      <c r="A249" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>492</v>
@@ -5541,12 +5661,12 @@
         <v>493</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
-      <c r="A250" s="3">
-        <v>1</v>
-      </c>
-      <c r="B250" s="3">
-        <v>26</v>
+    <row r="250" spans="1:4" ht="16.8">
+      <c r="A250" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>494</v>
@@ -5555,12 +5675,12 @@
         <v>495</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
-      <c r="A251" s="3">
-        <v>1</v>
-      </c>
-      <c r="B251" s="3">
-        <v>26</v>
+    <row r="251" spans="1:4" ht="16.8">
+      <c r="A251" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>583</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>496</v>
@@ -5569,12 +5689,12 @@
         <v>497</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
-      <c r="A252" s="3">
-        <v>1</v>
-      </c>
-      <c r="B252" s="3">
-        <v>27</v>
+    <row r="252" spans="1:4" ht="16.8">
+      <c r="A252" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>498</v>
@@ -5583,12 +5703,12 @@
         <v>499</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
-      <c r="A253" s="3">
-        <v>1</v>
-      </c>
-      <c r="B253" s="3">
-        <v>27</v>
+    <row r="253" spans="1:4" ht="16.8">
+      <c r="A253" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>422</v>
@@ -5597,12 +5717,12 @@
         <v>423</v>
       </c>
     </row>
-    <row r="254" spans="1:4">
-      <c r="A254" s="3">
-        <v>1</v>
-      </c>
-      <c r="B254" s="3">
-        <v>27</v>
+    <row r="254" spans="1:4" ht="16.8">
+      <c r="A254" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>500</v>
@@ -5611,12 +5731,12 @@
         <v>501</v>
       </c>
     </row>
-    <row r="255" spans="1:4">
-      <c r="A255" s="3">
-        <v>1</v>
-      </c>
-      <c r="B255" s="3">
-        <v>27</v>
+    <row r="255" spans="1:4" ht="16.8">
+      <c r="A255" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>502</v>
@@ -5625,12 +5745,12 @@
         <v>503</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
-      <c r="A256" s="3">
-        <v>1</v>
-      </c>
-      <c r="B256" s="3">
-        <v>27</v>
+    <row r="256" spans="1:4" ht="16.8">
+      <c r="A256" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>504</v>
@@ -5639,12 +5759,12 @@
         <v>505</v>
       </c>
     </row>
-    <row r="257" spans="1:4">
-      <c r="A257" s="3">
-        <v>1</v>
-      </c>
-      <c r="B257" s="3">
-        <v>27</v>
+    <row r="257" spans="1:4" ht="16.8">
+      <c r="A257" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>506</v>
@@ -5653,12 +5773,12 @@
         <v>507</v>
       </c>
     </row>
-    <row r="258" spans="1:4">
-      <c r="A258" s="3">
-        <v>1</v>
-      </c>
-      <c r="B258" s="3">
-        <v>27</v>
+    <row r="258" spans="1:4" ht="16.8">
+      <c r="A258" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>508</v>
@@ -5667,12 +5787,12 @@
         <v>509</v>
       </c>
     </row>
-    <row r="259" spans="1:4">
-      <c r="A259" s="3">
-        <v>1</v>
-      </c>
-      <c r="B259" s="3">
-        <v>27</v>
+    <row r="259" spans="1:4" ht="16.8">
+      <c r="A259" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>510</v>
@@ -5681,12 +5801,12 @@
         <v>511</v>
       </c>
     </row>
-    <row r="260" spans="1:4">
-      <c r="A260" s="3">
-        <v>1</v>
-      </c>
-      <c r="B260" s="3">
-        <v>27</v>
+    <row r="260" spans="1:4" ht="16.8">
+      <c r="A260" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>512</v>
@@ -5695,12 +5815,12 @@
         <v>513</v>
       </c>
     </row>
-    <row r="261" spans="1:4">
-      <c r="A261" s="3">
-        <v>1</v>
-      </c>
-      <c r="B261" s="3">
-        <v>27</v>
+    <row r="261" spans="1:4" ht="16.8">
+      <c r="A261" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>514</v>
@@ -5710,11 +5830,11 @@
       </c>
     </row>
     <row r="262" spans="1:4">
-      <c r="A262" s="3">
-        <v>1</v>
-      </c>
-      <c r="B262" s="3">
-        <v>28</v>
+      <c r="A262" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>516</v>
@@ -5724,11 +5844,11 @@
       </c>
     </row>
     <row r="263" spans="1:4">
-      <c r="A263" s="3">
-        <v>1</v>
-      </c>
-      <c r="B263" s="3">
-        <v>28</v>
+      <c r="A263" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>518</v>
@@ -5738,11 +5858,11 @@
       </c>
     </row>
     <row r="264" spans="1:4">
-      <c r="A264" s="3">
-        <v>1</v>
-      </c>
-      <c r="B264" s="3">
-        <v>28</v>
+      <c r="A264" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>520</v>
@@ -5752,11 +5872,11 @@
       </c>
     </row>
     <row r="265" spans="1:4">
-      <c r="A265" s="3">
-        <v>1</v>
-      </c>
-      <c r="B265" s="3">
-        <v>28</v>
+      <c r="A265" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>522</v>
@@ -5766,11 +5886,11 @@
       </c>
     </row>
     <row r="266" spans="1:4">
-      <c r="A266" s="3">
-        <v>1</v>
-      </c>
-      <c r="B266" s="3">
-        <v>28</v>
+      <c r="A266" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C266" s="3" t="s">
         <v>524</v>
@@ -5780,11 +5900,11 @@
       </c>
     </row>
     <row r="267" spans="1:4">
-      <c r="A267" s="3">
-        <v>1</v>
-      </c>
-      <c r="B267" s="3">
-        <v>28</v>
+      <c r="A267" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>526</v>
@@ -5794,11 +5914,11 @@
       </c>
     </row>
     <row r="268" spans="1:4">
-      <c r="A268" s="3">
-        <v>1</v>
-      </c>
-      <c r="B268" s="3">
-        <v>28</v>
+      <c r="A268" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>528</v>
@@ -5808,11 +5928,11 @@
       </c>
     </row>
     <row r="269" spans="1:4">
-      <c r="A269" s="3">
-        <v>1</v>
-      </c>
-      <c r="B269" s="3">
-        <v>28</v>
+      <c r="A269" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>530</v>
@@ -5822,11 +5942,11 @@
       </c>
     </row>
     <row r="270" spans="1:4">
-      <c r="A270" s="3">
-        <v>1</v>
-      </c>
-      <c r="B270" s="3">
-        <v>28</v>
+      <c r="A270" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>532</v>
@@ -5836,11 +5956,11 @@
       </c>
     </row>
     <row r="271" spans="1:4">
-      <c r="A271" s="3">
-        <v>1</v>
-      </c>
-      <c r="B271" s="3">
-        <v>28</v>
+      <c r="A271" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>585</v>
       </c>
       <c r="C271" s="3" t="s">
         <v>534</v>
@@ -5849,12 +5969,12 @@
         <v>535</v>
       </c>
     </row>
-    <row r="272" spans="1:4">
-      <c r="A272" s="3">
-        <v>1</v>
-      </c>
-      <c r="B272" s="3">
-        <v>29</v>
+    <row r="272" spans="1:4" ht="16.8">
+      <c r="A272" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>586</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>536</v>
@@ -5863,12 +5983,12 @@
         <v>537</v>
       </c>
     </row>
-    <row r="273" spans="1:4">
-      <c r="A273" s="3">
-        <v>1</v>
-      </c>
-      <c r="B273" s="3">
-        <v>29</v>
+    <row r="273" spans="1:4" ht="19.2">
+      <c r="A273" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>586</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>538</v>
@@ -5877,12 +5997,12 @@
         <v>539</v>
       </c>
     </row>
-    <row r="274" spans="1:4">
-      <c r="A274" s="3">
-        <v>1</v>
-      </c>
-      <c r="B274" s="3">
-        <v>29</v>
+    <row r="274" spans="1:4" ht="19.2">
+      <c r="A274" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>586</v>
       </c>
       <c r="C274" s="3" t="s">
         <v>540</v>
@@ -5891,12 +6011,12 @@
         <v>541</v>
       </c>
     </row>
-    <row r="275" spans="1:4">
-      <c r="A275" s="3">
-        <v>1</v>
-      </c>
-      <c r="B275" s="3">
-        <v>29</v>
+    <row r="275" spans="1:4" ht="19.2">
+      <c r="A275" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>586</v>
       </c>
       <c r="C275" s="3" t="s">
         <v>542</v>
@@ -5905,12 +6025,12 @@
         <v>543</v>
       </c>
     </row>
-    <row r="276" spans="1:4">
-      <c r="A276" s="3">
-        <v>1</v>
-      </c>
-      <c r="B276" s="3">
-        <v>29</v>
+    <row r="276" spans="1:4" ht="19.2">
+      <c r="A276" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>586</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>544</v>
@@ -5919,12 +6039,12 @@
         <v>545</v>
       </c>
     </row>
-    <row r="277" spans="1:4">
-      <c r="A277" s="3">
-        <v>1</v>
-      </c>
-      <c r="B277" s="3">
-        <v>29</v>
+    <row r="277" spans="1:4" ht="19.2">
+      <c r="A277" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>586</v>
       </c>
       <c r="C277" s="3" t="s">
         <v>546</v>
@@ -5933,12 +6053,12 @@
         <v>547</v>
       </c>
     </row>
-    <row r="278" spans="1:4">
-      <c r="A278" s="3">
-        <v>1</v>
-      </c>
-      <c r="B278" s="3">
-        <v>29</v>
+    <row r="278" spans="1:4" ht="19.2">
+      <c r="A278" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>586</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>548</v>
@@ -5947,12 +6067,12 @@
         <v>549</v>
       </c>
     </row>
-    <row r="279" spans="1:4">
-      <c r="A279" s="3">
-        <v>1</v>
-      </c>
-      <c r="B279" s="3">
-        <v>29</v>
+    <row r="279" spans="1:4" ht="19.2">
+      <c r="A279" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B279" s="8" t="s">
+        <v>586</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>550</v>
@@ -5961,12 +6081,12 @@
         <v>551</v>
       </c>
     </row>
-    <row r="280" spans="1:4">
-      <c r="A280" s="3">
-        <v>1</v>
-      </c>
-      <c r="B280" s="3">
-        <v>29</v>
+    <row r="280" spans="1:4" ht="19.2">
+      <c r="A280" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B280" s="8" t="s">
+        <v>586</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>552</v>
@@ -5975,12 +6095,12 @@
         <v>553</v>
       </c>
     </row>
-    <row r="281" spans="1:4">
-      <c r="A281" s="3">
-        <v>1</v>
-      </c>
-      <c r="B281" s="3">
-        <v>29</v>
+    <row r="281" spans="1:4" ht="19.2">
+      <c r="A281" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B281" s="8" t="s">
+        <v>586</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>554</v>
